--- a/WebMobileAPIAutomationGIT/target/classes/TestData/TestEnvironment/TestData.xlsx
+++ b/WebMobileAPIAutomationGIT/target/classes/TestData/TestEnvironment/TestData.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341E3F5F-3348-41D1-A7EE-D0FE4F3CBA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61928680-4997-494F-81BC-D7C35A4827BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="10" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="61">
   <si>
     <t>TC_ID</t>
   </si>
@@ -179,22 +179,25 @@
     <t>MANIPAL,DHARGAL,ZUARI NAGAR,HONDA,VERNA,CONCOLIM,KARWAR,PANJIM,KUNDAIM,MANGALORE,</t>
   </si>
   <si>
+    <t>KAIMARA (SHIMOGA),SAKKRAYAPATNA.,UDDEBORANAHALLI,AJJAMPURA,BIRUR,TARIKERE,KADUR,LINGADAHALLI,DEVANUR,BHADRAVATHI,MATTUR,CHANNAGIRI,HOSADURGA,SRIRAMPURA,ULVI,</t>
+  </si>
+  <si>
+    <t>KAIMARA (SHIMOGA),SAKKRAYAPATNA.,UDDEBORANAHALLI,AJJAMPURA,BIRUR,TARIKERE,KADUR,LINGADAHALLI,DEVANUR,BHADRAVATHI,ARSIKERE,CHANNAGIRI,HOSADURGA,SRIRAMPURA,MATTUR,ULVI,CHIKMAGALUR</t>
+  </si>
+  <si>
+    <t>KAIMARA (SHIMOGA),BHADRAVATI,SAKKRAYAPATNA.,UDDEBORANAHALLI,AJJAMPURA,BIRUR,TARIKERE,KADUR,LINGADAHALLI,DEVANUR,ARSIKERE,CHANNAGIRI,SRIRAMPURA,MATTUR,ULVI,CHIKMAGALUR</t>
+  </si>
+  <si>
     <t>WaitTimeInMilliAfterSearch</t>
   </si>
   <si>
     <t>URL</t>
   </si>
   <si>
-    <t>SearchTimeBeforeRows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.eye2serve.com:9001/sap/bc/ui5_ui5/ui2/ushell/shells/abap/FioriLaunchpad.html?saml2=disabled#Shell-home </t>
-  </si>
-  <si>
-    <t>zameer4827</t>
-  </si>
-  <si>
-    <t>KAIMARA (SHIMOGA),GANGUR,BIRUR,AJJAMPURA,CHANNAGIRI,BHADRAVATHI,KAREHALLI (BHADRA),ULVI.,SORAB,SAKKRAYAPATNA.,CHANDRAGUTTI,SHIVANI,TARIKERE,KADUR,LINGADAHALLI,DEVANUR,LAKKAVALLI,UDDEBORANAHALLI,SRIRAMPURA,BELGUR,HOSADURGA,CHICKJAJUR,CHIKMAGALUR,RANGANHALLI,SHIRALKOPPA,SHIMOGA,MATTUR,NAVALGUND,HUBLI,TOGARSI,KUMSI</t>
+    <t>https://www.eye2serve.com:9001/sap/bc/ui5_ui5/ui2/ushell/shells/abap/FioriLaunchpad.html#Shell-home</t>
+  </si>
+  <si>
+    <t>zameer54321</t>
   </si>
 </sst>
 </file>
@@ -678,40 +681,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="12.46484375" defaultRowHeight="15.75" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:AE8"/>
+  <sheetFormatPr defaultColWidth="12.44140625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.46484375" style="3" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="5.53125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="8.46484375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" style="3" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="5.5546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" style="3" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" style="3" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="13.53125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" style="3"/>
-    <col min="7" max="7" width="24.46484375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="6.86328125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" style="3"/>
+    <col min="7" max="7" width="24.44140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="6.88671875" style="3" customWidth="1"/>
     <col min="9" max="9" width="6.6640625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="12.46484375" style="3"/>
+    <col min="10" max="10" width="12.44140625" style="3"/>
     <col min="11" max="11" width="21.33203125" style="3" customWidth="1"/>
     <col min="12" max="12" width="6.6640625" style="3" customWidth="1"/>
-    <col min="13" max="13" width="7.19921875" style="3" customWidth="1"/>
-    <col min="14" max="14" width="12.46484375" style="3"/>
+    <col min="13" max="13" width="7.21875" style="3" customWidth="1"/>
+    <col min="14" max="14" width="12.44140625" style="3"/>
     <col min="15" max="15" width="17" style="3" customWidth="1"/>
-    <col min="16" max="16" width="6.53125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="6.5546875" style="3" customWidth="1"/>
     <col min="17" max="17" width="7.6640625" style="3" customWidth="1"/>
-    <col min="18" max="19" width="12.46484375" style="3"/>
-    <col min="20" max="20" width="5.86328125" style="3" customWidth="1"/>
+    <col min="18" max="19" width="12.44140625" style="3"/>
+    <col min="20" max="20" width="5.88671875" style="3" customWidth="1"/>
     <col min="21" max="21" width="7" style="3" customWidth="1"/>
-    <col min="22" max="23" width="12.46484375" style="3"/>
+    <col min="22" max="23" width="12.44140625" style="3"/>
     <col min="24" max="24" width="7.6640625" style="3" customWidth="1"/>
-    <col min="25" max="25" width="7.86328125" style="3" customWidth="1"/>
-    <col min="26" max="27" width="12.46484375" style="3"/>
-    <col min="28" max="28" width="36.796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="36.53125" style="3" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.88671875" style="3" customWidth="1"/>
+    <col min="26" max="27" width="12.44140625" style="3"/>
+    <col min="28" max="28" width="36.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="36.5546875" style="3" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="8.6640625" style="3" customWidth="1"/>
-    <col min="31" max="16384" width="12.46484375" style="3"/>
+    <col min="31" max="16384" width="12.44140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -791,7 +794,7 @@
         <v>26</v>
       </c>
       <c r="AA1" s="9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AB1" s="9" t="s">
         <v>27</v>
@@ -803,13 +806,10 @@
         <v>47</v>
       </c>
       <c r="AE1" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="AF1" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:32" s="11" customFormat="1" ht="409.5" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:31" s="11" customFormat="1" ht="296.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -823,7 +823,7 @@
         <v>2411780</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F2" s="6">
         <v>0</v>
@@ -850,22 +850,22 @@
         <v>40</v>
       </c>
       <c r="N2" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="P2" s="8">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="Q2" s="8">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="R2" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="T2" s="8">
         <v>30</v>
@@ -874,40 +874,37 @@
         <v>32</v>
       </c>
       <c r="V2" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W2" s="8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="X2" s="8">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Y2" s="8">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="Z2" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA2" s="6">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AB2" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2" s="12">
         <v>25000</v>
       </c>
       <c r="AE2" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF2" s="11">
-        <v>30</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:32" ht="189" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:31" ht="202.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -964,7 +961,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:32" ht="362.25" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:31" ht="374.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1021,7 +1018,7 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:32" ht="362.25" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:31" ht="374.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1078,7 +1075,7 @@
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
     </row>
-    <row r="6" spans="1:32" ht="362.25" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:31" ht="374.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -1135,7 +1132,7 @@
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
     </row>
-    <row r="7" spans="1:32" ht="378" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:31" ht="405.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -1192,7 +1189,7 @@
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
     </row>
-    <row r="8" spans="1:32" ht="362.25" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:31" ht="374.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
@@ -1253,7 +1250,7 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="zrl777@2024" xr:uid="{966C0453-0060-45F4-8DDC-A36C4D21D1AB}"/>
-    <hyperlink ref="AE2" r:id="rId2" location="Shell-home " xr:uid="{9DB233C2-AE14-4268-A2E0-B52B03463E63}"/>
+    <hyperlink ref="AE2" r:id="rId2" location="Shell-home" xr:uid="{9DB233C2-AE14-4268-A2E0-B52B03463E63}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
